--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A105CE83-C5AD-4BB1-ADFB-51D8DB3B660D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BB2428-53D4-44F1-88FE-38F3AB366FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43035" yWindow="4050" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>#1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,22 +99,6 @@
   </si>
   <si>
     <t>short_level [V]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100n</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c19 r6 위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>330n</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -192,7 +187,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>44824</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
@@ -209,8 +204,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="609600"/>
-          <a:ext cx="819150" cy="2305050"/>
+          <a:off x="2383491" y="619685"/>
+          <a:ext cx="507627" cy="2360519"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -717,39 +712,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:U26"/>
+  <dimension ref="B2:P26"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.8125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="7.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.4375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="6.3125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="6.8125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="1">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1">
+        <v>27</v>
+      </c>
       <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="T3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.6">
+      <c r="C3" s="1">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
@@ -783,17 +786,23 @@
       <c r="P4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.6">
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="C5" s="1">
+        <v>0.255</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.247</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.34499999999999997</v>
+      </c>
       <c r="K5" s="3">
         <v>8</v>
       </c>
@@ -813,13 +822,25 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B6" s="2">
         <v>0.4</v>
       </c>
+      <c r="C6" s="1">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.437</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.42799999999999999</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="I6" s="1">
+        <v>0.51700000000000002</v>
+      </c>
       <c r="K6" s="2">
         <v>32</v>
       </c>
@@ -839,45 +860,129 @@
         <v>0.34899999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B7" s="2">
         <v>0.5</v>
       </c>
+      <c r="C7" s="1">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.52700000000000002</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="I7" s="1">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B8" s="2">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C8" s="1">
+        <v>0.627</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.626</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.71599999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B9" s="2">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C9" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B10" s="2">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C10" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B11" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C11" s="1">
+        <v>1.03</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.0189999999999999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B12" s="2">
         <v>1.1499999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C12" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B13" s="2">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="C13" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.4179999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.6">
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,51 +1008,148 @@
       <c r="B19" s="2">
         <v>3</v>
       </c>
+      <c r="C19" s="1">
+        <v>3.49</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3.51</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3.38</v>
+      </c>
       <c r="G19" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2.64</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B20" s="2">
         <v>4</v>
       </c>
+      <c r="C20" s="1">
+        <v>4.68</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4.5599999999999996</v>
+      </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3.67</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B21" s="2">
         <v>6</v>
       </c>
+      <c r="C21" s="1">
+        <v>6.6239999999999997</v>
+      </c>
+      <c r="D21" s="1">
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="E21" s="1">
+        <v>6.49</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5.75</v>
+      </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B22" s="2">
         <v>8</v>
       </c>
+      <c r="C22" s="1">
+        <v>8.5559999999999992</v>
+      </c>
+      <c r="D22" s="1">
+        <v>8.42</v>
+      </c>
+      <c r="E22" s="1">
+        <v>8.8659999999999997</v>
+      </c>
+      <c r="I22" s="1">
+        <v>7.53</v>
+      </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B23" s="2">
         <v>12</v>
       </c>
+      <c r="C23" s="1">
+        <v>13.44</v>
+      </c>
+      <c r="D23" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>13.46</v>
+      </c>
+      <c r="I23" s="1">
+        <v>11.388</v>
+      </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B24" s="2">
         <v>16</v>
       </c>
+      <c r="C24" s="1">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="D24" s="1">
+        <v>17.3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>17.62</v>
+      </c>
+      <c r="I24" s="1">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B25" s="2">
         <v>24</v>
       </c>
+      <c r="C25" s="1">
+        <v>25.76</v>
+      </c>
+      <c r="D25" s="1">
+        <v>25.33</v>
+      </c>
+      <c r="E25" s="1">
+        <v>25.78</v>
+      </c>
+      <c r="I25" s="1">
+        <v>23.71</v>
+      </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.6">
       <c r="B26" s="2">
         <v>36</v>
       </c>
+      <c r="C26" s="1">
+        <v>37.35</v>
+      </c>
+      <c r="D26" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>37.79</v>
+      </c>
+      <c r="I26" s="1">
+        <v>36.17</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BB2428-53D4-44F1-88FE-38F3AB366FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC4A210-9516-4BB0-A019-1F8503309D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43035" yWindow="4050" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -446,6 +446,50 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>630148</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>186818</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8CB3B46-7DC8-43B9-B4D9-5422AC93390D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11183471" y="224118"/>
+          <a:ext cx="8832853" cy="3772700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_fault_detector_250404.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC4A210-9516-4BB0-A019-1F8503309D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D7AEB6-348A-4F8D-AFB1-2EA9A1C0624D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="5760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>#1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -99,6 +99,14 @@
   </si>
   <si>
     <t>short_level [V]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duty 100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duty 50%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +130,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -158,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -457,7 +474,7 @@
       <xdr:col>29</xdr:col>
       <xdr:colOff>630148</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>186818</xdr:rowOff>
+      <xdr:rowOff>183643</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -488,6 +505,140 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="직사각형 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86AC5376-F1D5-453C-9DFB-19504A92B5A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2562785" y="3757332"/>
+          <a:ext cx="552077" cy="2145927"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="화살표: 오른쪽 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186C2C8E-C45E-48A1-BB3F-537C7B3132A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3381562" y="4539503"/>
+          <a:ext cx="1453403" cy="562535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -756,25 +907,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P26"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="B2:V26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="7.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="13.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="6.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
@@ -788,7 +939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.45">
       <c r="C3" s="1">
         <v>31</v>
       </c>
@@ -796,7 +947,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
@@ -831,7 +982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
@@ -866,7 +1017,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B6" s="2">
         <v>0.4</v>
       </c>
@@ -904,7 +1055,7 @@
         <v>0.34899999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B7" s="2">
         <v>0.5</v>
       </c>
@@ -924,7 +1075,7 @@
         <v>0.61699999999999999</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B8" s="2">
         <v>0.6</v>
       </c>
@@ -941,7 +1092,7 @@
         <v>0.71599999999999997</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B9" s="2">
         <v>0.7</v>
       </c>
@@ -958,7 +1109,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B10" s="2">
         <v>0.85</v>
       </c>
@@ -975,7 +1126,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B11" s="2">
         <v>1</v>
       </c>
@@ -992,7 +1143,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B12" s="2">
         <v>1.1499999999999999</v>
       </c>
@@ -1009,7 +1160,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B13" s="2">
         <v>1.3</v>
       </c>
@@ -1026,12 +1177,23 @@
         <v>1.4179999999999999</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K16" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.45">
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1047,8 +1209,23 @@
       <c r="I18" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B19" s="2">
         <v>3</v>
       </c>
@@ -1067,8 +1244,26 @@
       <c r="I19" s="1">
         <v>2.64</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K19" s="2">
+        <v>3</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2.5880000000000001</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2.6659999999999999</v>
+      </c>
+      <c r="N19" s="1">
+        <v>3.17</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R19" s="1">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B20" s="2">
         <v>4</v>
       </c>
@@ -1087,8 +1282,23 @@
       <c r="I20" s="1">
         <v>3.67</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K20" s="2">
+        <v>4</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4.101</v>
+      </c>
+      <c r="M20" s="1">
+        <v>4.17</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="1">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B21" s="2">
         <v>6</v>
       </c>
@@ -1104,8 +1314,20 @@
       <c r="I21" s="1">
         <v>5.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K21" s="2">
+        <v>6</v>
+      </c>
+      <c r="L21" s="1">
+        <v>6.3719999999999999</v>
+      </c>
+      <c r="M21" s="1">
+        <v>6.55</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B22" s="2">
         <v>8</v>
       </c>
@@ -1121,8 +1343,20 @@
       <c r="I22" s="1">
         <v>7.53</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K22" s="2">
+        <v>8</v>
+      </c>
+      <c r="L22" s="1">
+        <v>8.4559999999999995</v>
+      </c>
+      <c r="M22" s="1">
+        <v>8.6620000000000008</v>
+      </c>
+      <c r="R22" s="1">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B23" s="2">
         <v>12</v>
       </c>
@@ -1138,8 +1372,20 @@
       <c r="I23" s="1">
         <v>11.388</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K23" s="2">
+        <v>12</v>
+      </c>
+      <c r="L23" s="1">
+        <v>10.976000000000001</v>
+      </c>
+      <c r="M23" s="1">
+        <v>11.288</v>
+      </c>
+      <c r="R23" s="1">
+        <v>11.388</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B24" s="2">
         <v>16</v>
       </c>
@@ -1155,8 +1401,20 @@
       <c r="I24" s="1">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K24" s="2">
+        <v>16</v>
+      </c>
+      <c r="L24" s="1">
+        <v>15.722</v>
+      </c>
+      <c r="M24" s="1">
+        <v>16.093</v>
+      </c>
+      <c r="R24" s="1">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B25" s="2">
         <v>24</v>
       </c>
@@ -1172,8 +1430,23 @@
       <c r="I25" s="1">
         <v>23.71</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.6">
+      <c r="K25" s="2">
+        <v>24</v>
+      </c>
+      <c r="L25" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="M25" s="1">
+        <v>25.343</v>
+      </c>
+      <c r="R25" s="1">
+        <v>23.71</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B26" s="2">
         <v>36</v>
       </c>
@@ -1188,6 +1461,22 @@
       </c>
       <c r="I26" s="1">
         <v>36.17</v>
+      </c>
+      <c r="K26" s="2">
+        <v>36</v>
+      </c>
+      <c r="L26" s="1">
+        <v>36.866999999999997</v>
+      </c>
+      <c r="M26" s="1">
+        <v>36.9</v>
+      </c>
+      <c r="R26" s="1">
+        <v>36.17</v>
+      </c>
+      <c r="V26" s="1">
+        <f>1.5/V25</f>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
